--- a/Audit_Work_Program.xlsx
+++ b/Audit_Work_Program.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james.goh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mazarsglobalcloud-my.sharepoint.com/personal/yi-xiu_leng_mazars_com_sg/Documents/Documents/00. Digital Transformation/Madman/Financials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CADB1B5-E5E4-4256-B70E-2F01A8271AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{7CADB1B5-E5E4-4256-B70E-2F01A8271AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCDE23DB-ACF9-420A-81EA-7645CC0CD789}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
   <si>
     <t>Sub-process</t>
   </si>
@@ -717,6 +717,69 @@
 BOMs and material master prices
 Labour rates and routing reports
 Overhead rate memo</t>
+  </si>
+  <si>
+    <t>Sales &amp; Pricing</t>
+  </si>
+  <si>
+    <t>Pricing master data governance</t>
+  </si>
+  <si>
+    <t>Incorrect or unauthorized list price/discount configurations lead to margin erosion and misstated revenue.</t>
+  </si>
+  <si>
+    <t>Contract &amp; rebate/chargeback setup (GPO/Distributor)</t>
+  </si>
+  <si>
+    <t>Misconfigured contract terms or tier eligibility causes over/under accruals and incorrect net pricing; compliance/fraud risk.</t>
+  </si>
+  <si>
+    <t>Sales order entry &amp; price execution</t>
+  </si>
+  <si>
+    <t>Invoiced prices deviate from approved terms due to manual overrides, wrong ship-to, or free goods; revenue misstatement.</t>
+  </si>
+  <si>
+    <t>Revenue deductions – rebates/chargebacks processing</t>
+  </si>
+  <si>
+    <t>Incomplete or inaccurate claims cause misstated deductions and margin distortion; duplicate or ineligible claims processed.</t>
+  </si>
+  <si>
+    <t>Accruals for rebates/chargebacks</t>
+  </si>
+  <si>
+    <t>Under/over-accruals drive incorrect period revenue and margins; unsupported manual journals.</t>
+  </si>
+  <si>
+    <t>Side agreements &amp; post-invoice credits</t>
+  </si>
+  <si>
+    <t>Unrecorded price concessions through side letters, free goods, or after-the-fact credits bypass approvals and recognition rules.</t>
+  </si>
+  <si>
+    <t>Returns, RMAs &amp; restocking fees</t>
+  </si>
+  <si>
+    <t>Unapproved returns or incorrect restocking fee handling results in overstatements of deductions or hidden concessions.</t>
+  </si>
+  <si>
+    <t>Customer/GPO membership validation</t>
+  </si>
+  <si>
+    <t>Charging contracted prices to ineligible members creates undue deductions and compliance issues.</t>
+  </si>
+  <si>
+    <t>Segregation of duties (SoD) &amp; access</t>
+  </si>
+  <si>
+    <t>Users can create/approve prices and also post credits or journals, enabling fraud or error.</t>
+  </si>
+  <si>
+    <t>Analytics &amp; monitoring of margin</t>
+  </si>
+  <si>
+    <t>Anomalies in invoice line margin not detected timely due to lack of monitoring.</t>
   </si>
 </sst>
 </file>
@@ -785,9 +848,6 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -798,6 +858,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1101,155 +1164,265 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="92.36328125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="184" style="3" customWidth="1"/>
-    <col min="6" max="6" width="64" style="3" customWidth="1"/>
+    <col min="1" max="1" width="17.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.81640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="54.6328125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40" style="2" customWidth="1"/>
+    <col min="5" max="5" width="154.36328125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="64" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" ht="398" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="398" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="4" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="4" customFormat="1" ht="109" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" s="3" customFormat="1" ht="109" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="4" customFormat="1" ht="254" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" s="3" customFormat="1" ht="254" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="4" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="290" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="4" customFormat="1" ht="261" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" s="3" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Audit_Work_Program.xlsx
+++ b/Audit_Work_Program.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mazarsglobalcloud-my.sharepoint.com/personal/yi-xiu_leng_mazars_com_sg/Documents/Documents/00. Digital Transformation/Madman/Financials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{7CADB1B5-E5E4-4256-B70E-2F01A8271AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCDE23DB-ACF9-420A-81EA-7645CC0CD789}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{7CADB1B5-E5E4-4256-B70E-2F01A8271AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F4A4B80-0577-4009-95D7-6A5B47296525}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
   <si>
     <t>Sub-process</t>
   </si>
@@ -780,6 +780,279 @@
   </si>
   <si>
     <t>Anomalies in invoice line margin not detected timely due to lack of monitoring.</t>
+  </si>
+  <si>
+    <t>Travel &amp; Entertainment (T&amp;E)</t>
+  </si>
+  <si>
+    <t>False, duplicate, unsupported or non‑business related expenses may result in financial misstatement, policy non‑compliance and potential fraud.</t>
+  </si>
+  <si>
+    <t>Employees must submit T&amp;E claims with proper receipts and clear business purpose; approvals required from Reporting Manager and Finance; policy limits apply and exception reports are reviewed monthly.</t>
+  </si>
+  <si>
+    <t>Gifts &amp; Hospitality</t>
+  </si>
+  <si>
+    <t>Undeclared, excessive or inappropriate gifts and hospitality may create conflicts of interest, bribery risk or breach of policy.</t>
+  </si>
+  <si>
+    <t>Gifts and hospitality above threshold must be declared; approval from Manager/Compliance required; a register is maintained and reviewed periodically.</t>
+  </si>
+  <si>
+    <t>Corporate Credit Card</t>
+  </si>
+  <si>
+    <t>Personal charges, unsupported expenditures or insufficient oversight may result in misuse of corporate resources.</t>
+  </si>
+  <si>
+    <t>Corporate cards are issued to authorized personnel; monthly statements require review by employee and approver; receipts must be retained and Finance performs periodic checks.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Walkthrough and understanding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1) Perform walkthrough with Compliance to understand gift declaration and approval processes.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Register completeness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1) Obtain the gifts &amp; hospitality register.
+2) Perform completeness checks using hospitality expenses, keyword search and high‑risk employee roles.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sample testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1) Verify business justification, value reasonableness, supporting documents and approvals.</t>
+    </r>
+  </si>
+  <si>
+    <t>PTP - Employee Expenditure</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Walkthrough and understanding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1) Obtain cardholder listing and walkthrough issuance and review procedures.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Statement testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1) Select monthly card statements.
+2) Verify receipts, business purpose, policy compliance, approvals and any personal reimbursements.
+3) Review unusual spending patterns.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Monitoring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1) Assess Finance's exception review process.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Walkthrough and understanding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1) Perform a walkthrough with Finance to understand T&amp;E submission, review and approval workflow.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T&amp;E claim review</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1) Obtain full listing of T&amp;E claims for the audit period.
+2) Select risk‑based samples, mainly on abnormal amounts or suspicious transactions.
+3) Perform duplicate check across T&amp;E, corporate card and reimbursements.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Monitoring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1) Obtain T&amp;E exception reports.
+2) Verify reviews and follow‑up actions.</t>
+    </r>
+  </si>
+  <si>
+    <t>Gifts Policy
+Gifts register
+Hospitality report with approval status
+Employee list</t>
+  </si>
+  <si>
+    <t>T&amp;E Policy
+Monthly travel expense reports with approval status
+Employee list
+Exception reports</t>
+  </si>
+  <si>
+    <t>Corporate Card Policy
+Cardholder listing
+Monthly statements
+Approvals</t>
   </si>
 </sst>
 </file>
@@ -845,22 +1118,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1164,15 +1431,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.81640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="54.6328125" style="2" customWidth="1"/>
     <col min="4" max="4" width="40" style="2" customWidth="1"/>
-    <col min="5" max="5" width="154.36328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="103.90625" style="2" customWidth="1"/>
     <col min="6" max="6" width="64" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1195,233 +1463,293 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" ht="398" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" ht="398" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="3" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:6" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="3" customFormat="1" ht="109" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:6" ht="109" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="3" customFormat="1" ht="254" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:6" ht="254" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="3" customFormat="1" ht="290" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:6" ht="290" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="3" customFormat="1" ht="275.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:6" ht="326" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:6" ht="187.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="140.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="157" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="12" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+    <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C13" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+    <row r="14" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+    <row r="15" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C15" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+    <row r="16" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C16" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+    <row r="17" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C17" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+    <row r="18" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C18" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+    <row r="19" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C19" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+    <row r="20" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>57</v>
       </c>
     </row>
